--- a/data/derived-data/megatrends_metadata.xlsx
+++ b/data/derived-data/megatrends_metadata.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
   <si>
     <t>Name</t>
   </si>
@@ -619,6 +619,54 @@
   </si>
   <si>
     <t xml:space="preserve">Productivism shift</t>
+  </si>
+  <si>
+    <t>FRAISLOCAL_N_2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of local selling shops or producers listed in www.fraisetlocal.fr</t>
+  </si>
+  <si>
+    <t>Fraisetlocal</t>
+  </si>
+  <si>
+    <t>02o_get_localfarms.R</t>
+  </si>
+  <si>
+    <t>FRAISLOCAL_SHOPS_N_2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of local selling shops listed in www.fraisetlocal.fr</t>
+  </si>
+  <si>
+    <t>FRAISLOCAL_PROD_N_2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of local agricultural producers listed in www.fraisetlocal.fr</t>
+  </si>
+  <si>
+    <t>AGTOURISM_N_2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of agrotourism locations from labels "agriculture biologique", "Bienvenue a la ferme", "Vignobles et Decouvertes, "Accueil Paysan".</t>
+  </si>
+  <si>
+    <t>DataTourisme</t>
+  </si>
+  <si>
+    <t>AMAP_DIST_KM_2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distance to closest AMAP (Association pour le Maintien d’une Agriculture Paysanne) listed in avenir-bio.fr</t>
+  </si>
+  <si>
+    <t>avenir-bio</t>
+  </si>
+  <si>
+    <t>02p_get_amap.R</t>
+  </si>
+  <si>
+    <t>communes</t>
   </si>
 </sst>
 </file>
@@ -697,7 +745,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="31">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -776,25 +824,11 @@
     <xf fontId="8" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2150,7 +2184,7 @@
       <c r="C30" s="5">
         <v>2020</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="D30" s="4" t="s">
         <v>49</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -2159,12 +2193,12 @@
       <c r="F30" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="G30" s="28" t="s">
+      <c r="G30" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
-      <c r="J30" s="28" t="s">
+      <c r="J30" s="4" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2224,7 +2258,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" ht="14.25">
+    <row r="33" ht="25.5">
       <c r="A33" t="s">
         <v>120</v>
       </c>
@@ -2260,7 +2294,7 @@
       <c r="A34" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B34" s="29" t="s">
+      <c r="B34" s="5" t="s">
         <v>124</v>
       </c>
       <c r="C34" s="12">
@@ -2321,16 +2355,16 @@
       </c>
     </row>
     <row r="36" s="0" customFormat="1" ht="25.5">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B36" s="30" t="s">
+      <c r="B36" s="12" t="s">
         <v>129</v>
       </c>
       <c r="C36">
         <v>2020</v>
       </c>
-      <c r="D36" s="30" t="s">
+      <c r="D36" s="12" t="s">
         <v>27</v>
       </c>
       <c r="E36" s="1" t="s">
@@ -2350,13 +2384,13 @@
       <c r="A37" t="s">
         <v>130</v>
       </c>
-      <c r="B37" s="30" t="s">
+      <c r="B37" s="12" t="s">
         <v>131</v>
       </c>
       <c r="C37">
         <v>2020</v>
       </c>
-      <c r="D37" s="30" t="s">
+      <c r="D37" s="12" t="s">
         <v>132</v>
       </c>
       <c r="E37" s="1" t="s">
@@ -2373,16 +2407,16 @@
       </c>
     </row>
     <row r="38" s="0" customFormat="1" ht="25.5">
-      <c r="A38" s="30" t="s">
+      <c r="A38" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B38" s="30" t="s">
+      <c r="B38" s="12" t="s">
         <v>134</v>
       </c>
       <c r="C38">
         <v>2020</v>
       </c>
-      <c r="D38" s="30" t="s">
+      <c r="D38" s="12" t="s">
         <v>132</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -2399,16 +2433,16 @@
       </c>
     </row>
     <row r="39" s="0" customFormat="1" ht="25.5">
-      <c r="A39" s="30" t="s">
+      <c r="A39" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B39" s="30" t="s">
+      <c r="B39" s="12" t="s">
         <v>136</v>
       </c>
       <c r="C39" s="4">
         <v>2020</v>
       </c>
-      <c r="D39" s="30" t="s">
+      <c r="D39" s="12" t="s">
         <v>137</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -2425,16 +2459,16 @@
       </c>
     </row>
     <row r="40" s="0" customFormat="1" ht="25.5">
-      <c r="A40" s="30" t="s">
+      <c r="A40" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B40" s="30" t="s">
+      <c r="B40" s="12" t="s">
         <v>139</v>
       </c>
       <c r="C40">
         <v>2020</v>
       </c>
-      <c r="D40" s="30" t="s">
+      <c r="D40" s="12" t="s">
         <v>140</v>
       </c>
       <c r="E40" s="1" t="s">
@@ -2451,16 +2485,16 @@
       </c>
     </row>
     <row r="41" s="0" customFormat="1" ht="25.5">
-      <c r="A41" s="30" t="s">
+      <c r="A41" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B41" s="30" t="s">
+      <c r="B41" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="12">
         <v>2010</v>
       </c>
-      <c r="D41" s="32" t="s">
+      <c r="D41" s="12" t="s">
         <v>27</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -2469,24 +2503,24 @@
       <c r="F41" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="G41" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="J41" s="33" t="s">
+      <c r="G41" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J41" s="4" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="42" s="0" customFormat="1" ht="25.5">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B42" s="30" t="s">
+      <c r="B42" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="12">
         <v>2010</v>
       </c>
-      <c r="D42" s="32" t="s">
+      <c r="D42" s="12" t="s">
         <v>27</v>
       </c>
       <c r="E42" s="1" t="s">
@@ -2495,10 +2529,10 @@
       <c r="F42" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="G42" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="J42" s="28" t="s">
+      <c r="G42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" s="4" t="s">
         <v>143</v>
       </c>
     </row>
@@ -2506,7 +2540,7 @@
       <c r="A43" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B43" s="34" t="s">
+      <c r="B43" s="28" t="s">
         <v>147</v>
       </c>
       <c r="C43" t="s">
@@ -2529,7 +2563,7 @@
       <c r="A44" t="s">
         <v>151</v>
       </c>
-      <c r="B44" s="34" t="s">
+      <c r="B44" s="28" t="s">
         <v>152</v>
       </c>
       <c r="C44" t="s">
@@ -2736,7 +2770,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="52" ht="14.25">
+    <row r="52" ht="28.5">
       <c r="A52" s="4" t="s">
         <v>174</v>
       </c>
@@ -2765,7 +2799,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="53" ht="14.25">
+    <row r="53" ht="28.5">
       <c r="A53" s="4" t="s">
         <v>177</v>
       </c>
@@ -2794,7 +2828,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="54" ht="14.25">
+    <row r="54" ht="28.5">
       <c r="A54" s="4" t="s">
         <v>184</v>
       </c>
@@ -2824,7 +2858,7 @@
       </c>
     </row>
     <row r="55" ht="14.25">
-      <c r="A55" s="35" t="s">
+      <c r="A55" s="4" t="s">
         <v>190</v>
       </c>
       <c r="B55" t="s">
@@ -2836,10 +2870,10 @@
       <c r="D55" t="s">
         <v>192</v>
       </c>
-      <c r="E55" s="36" t="s">
+      <c r="E55" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F55" s="36" t="s">
+      <c r="F55" s="1" t="s">
         <v>194</v>
       </c>
       <c r="G55" s="4" t="s">
@@ -2853,7 +2887,7 @@
       <c r="A56" t="s">
         <v>195</v>
       </c>
-      <c r="B56" s="30" t="s">
+      <c r="B56" s="12" t="s">
         <v>196</v>
       </c>
       <c r="C56" s="4">
@@ -2876,6 +2910,106 @@
       </c>
       <c r="J56" t="s">
         <v>168</v>
+      </c>
+    </row>
+    <row r="57" ht="14.25">
+      <c r="A57" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B57" t="s">
+        <v>199</v>
+      </c>
+      <c r="C57">
+        <v>2025</v>
+      </c>
+      <c r="E57" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="F57" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="J57" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="58" ht="14.25">
+      <c r="A58" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B58" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="C58" s="4">
+        <v>2025</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J58" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="59" ht="14.25">
+      <c r="A59" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B59" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C59" s="4">
+        <v>2025</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J59" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="60" ht="14.25">
+      <c r="A60" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B60" t="s">
+        <v>207</v>
+      </c>
+      <c r="C60">
+        <v>2025</v>
+      </c>
+      <c r="E60" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J60" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="61" ht="14.25">
+      <c r="A61" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B61" t="s">
+        <v>210</v>
+      </c>
+      <c r="C61">
+        <v>2026</v>
+      </c>
+      <c r="E61" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="J61" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/data/derived-data/megatrends_metadata.xlsx
+++ b/data/derived-data/megatrends_metadata.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="216">
   <si>
     <t>Name</t>
   </si>
@@ -227,12 +227,6 @@
 Changes in farming practices</t>
   </si>
   <si>
-    <t>PESTICIDE_NPIXELS_2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of pixels within Rigal and Perrot (for internal checks only)</t>
-  </si>
-  <si>
     <t>PESTICIDE_TII_2022</t>
   </si>
   <si>
@@ -667,6 +661,18 @@
   </si>
   <si>
     <t>communes</t>
+  </si>
+  <si>
+    <t>BIOPRO_N_2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of companies with an organic certification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agence bio</t>
+  </si>
+  <si>
+    <t>02q_get_bio_pro.R</t>
   </si>
 </sst>
 </file>
@@ -825,10 +831,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1719,16 +1727,17 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" s="0" customFormat="1" ht="25.5">
+    <row r="14" s="0" customFormat="1" ht="28.5">
       <c r="A14" s="4" t="s">
         <v>68</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="4">
         <v>2022</v>
       </c>
+      <c r="D14" s="12"/>
       <c r="E14" s="18" t="s">
         <v>62</v>
       </c>
@@ -1740,7 +1749,7 @@
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="12" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1754,7 +1763,9 @@
       <c r="C15" s="4">
         <v>2022</v>
       </c>
-      <c r="D15" s="12"/>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
       <c r="E15" s="18" t="s">
         <v>62</v>
       </c>
@@ -1766,154 +1777,154 @@
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
-      <c r="J15" s="12" t="s">
+      <c r="J15" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="16" s="0" customFormat="1" ht="28.5">
+    <row r="16" s="0" customFormat="1" ht="25.5">
       <c r="A16" s="4" t="s">
         <v>72</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="4">
-        <v>2022</v>
+      <c r="C16">
+        <v>2025</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>77</v>
+      </c>
       <c r="J16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" s="0" customFormat="1" ht="25.5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" s="0" customFormat="1" ht="28.5">
       <c r="A17" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C17">
         <v>2025</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>78</v>
-      </c>
       <c r="G17" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="I17" s="19" t="s">
-        <v>79</v>
-      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
       <c r="J17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="18" s="0" customFormat="1" ht="28.5">
-      <c r="A18" s="4" t="s">
+    <row r="18" s="0" customFormat="1" ht="25.5">
+      <c r="A18" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C18">
-        <v>2025</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" t="s">
-        <v>46</v>
+      <c r="C18" s="24">
+        <v>2023</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="19" s="0" customFormat="1" ht="25.5">
       <c r="A19" s="23" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C19" s="24">
         <v>2023</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J19" s="24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" s="0" customFormat="1" ht="25.5">
-      <c r="A20" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="B20" s="20" t="s">
+    <row r="20" s="0" customFormat="1" ht="42.75">
+      <c r="A20" s="24" t="s">
         <v>88</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>89</v>
       </c>
       <c r="C20" s="24">
         <v>2023</v>
       </c>
+      <c r="D20" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E20" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="21" t="s">
-        <v>89</v>
-      </c>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
       <c r="J20" s="24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" s="0" customFormat="1" ht="42.75">
+    <row r="21" s="1" customFormat="1" ht="14.25">
       <c r="A21" s="24" t="s">
         <v>90</v>
       </c>
@@ -1924,16 +1935,16 @@
         <v>2023</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
@@ -1942,23 +1953,23 @@
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="14.25">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="23" t="s">
         <v>92</v>
       </c>
       <c r="B22" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="1">
         <v>2023</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>21</v>
@@ -1970,71 +1981,75 @@
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="14.25">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="24">
         <v>2023</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="J23" s="24" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="14.25">
-      <c r="A24" s="24" t="s">
-        <v>96</v>
+      <c r="A24" s="23" t="s">
+        <v>97</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C24" s="24">
         <v>2023</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>15</v>
       </c>
       <c r="H24" s="21" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="I24" s="21" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J24" s="24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="14.25">
-      <c r="A25" s="23" t="s">
-        <v>99</v>
+    <row r="25" s="1" customFormat="1" ht="25.5">
+      <c r="A25" s="24" t="s">
+        <v>101</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C25" s="24">
         <v>2023</v>
@@ -2043,99 +2058,95 @@
         <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H25" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="I25" s="21" t="s">
-        <v>102</v>
-      </c>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
       <c r="J25" s="24" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="25.5">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="24">
-        <v>2023</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>12</v>
+      <c r="C26">
+        <v>2020</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="25.5">
-      <c r="A27" s="17" t="s">
         <v>105</v>
       </c>
+      <c r="F26" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I26" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="J26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="14.25">
+      <c r="A27" s="4" t="s">
+        <v>108</v>
+      </c>
       <c r="B27" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C27">
         <v>2020</v>
       </c>
-      <c r="D27" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>107</v>
+      <c r="E27" s="24" t="s">
+        <v>105</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
       </c>
-      <c r="H27" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="I27" s="19" t="s">
-        <v>109</v>
-      </c>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
       <c r="J27" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="14.25">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="5">
         <v>2020</v>
       </c>
-      <c r="E28" s="24" t="s">
-        <v>107</v>
+      <c r="D28" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="F28" s="27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G28" t="s">
         <v>15</v>
@@ -2156,26 +2167,26 @@
       <c r="C29" s="5">
         <v>2020</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="4" t="s">
         <v>49</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="G29" t="s">
+        <v>106</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>15</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
-      <c r="J29" t="s">
+      <c r="J29" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="14.25">
-      <c r="A30" s="14" t="s">
+    <row r="30" s="0" customFormat="1" ht="14.25">
+      <c r="A30" s="22" t="s">
         <v>114</v>
       </c>
       <c r="B30" s="18" t="s">
@@ -2184,54 +2195,54 @@
       <c r="C30" s="5">
         <v>2020</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>107</v>
-      </c>
+      <c r="D30" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" s="1"/>
       <c r="F30" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I30" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="J30" s="12"/>
+    </row>
+    <row r="31" s="0" customFormat="1" ht="14.25">
+      <c r="A31" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" s="12">
+        <v>2020</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F31" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="12" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="31" s="0" customFormat="1" ht="14.25">
-      <c r="A31" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="C31" s="5">
-        <v>2020</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="E31" s="1"/>
-      <c r="F31" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H31" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="I31" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="J31" s="12"/>
-    </row>
-    <row r="32" s="0" customFormat="1" ht="14.25">
-      <c r="A32" s="4" t="s">
+    <row r="32" ht="25.5">
+      <c r="A32" t="s">
         <v>118</v>
       </c>
       <c r="B32" s="5" t="s">
@@ -2244,118 +2255,116 @@
         <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F32" s="27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G32" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
+      <c r="H32" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I32" s="19" t="s">
+        <v>120</v>
+      </c>
       <c r="J32" s="12" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" ht="25.5">
-      <c r="A33" t="s">
-        <v>120</v>
+    <row r="33" s="0" customFormat="1" ht="25.5">
+      <c r="A33" s="17" t="s">
+        <v>121</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C33" s="12">
         <v>2020</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F33" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I33" s="19" t="s">
         <v>107</v>
-      </c>
-      <c r="F33" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H33" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="I33" s="19" t="s">
-        <v>122</v>
       </c>
       <c r="J33" s="12" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="34" s="0" customFormat="1" ht="25.5">
-      <c r="A34" s="17" t="s">
-        <v>123</v>
+      <c r="A34" t="s">
+        <v>124</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C34" s="12">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F34" s="27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>15</v>
       </c>
       <c r="H34" s="19" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I34" s="19" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="J34" s="12" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="35" s="0" customFormat="1" ht="25.5">
-      <c r="A35" t="s">
+      <c r="A35" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="C35" s="12">
-        <v>2010</v>
+      <c r="C35">
+        <v>2020</v>
       </c>
       <c r="D35" s="12" t="s">
         <v>27</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F35" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H35" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="I35" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="J35" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G35" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="36" s="0" customFormat="1" ht="25.5">
-      <c r="A36" s="12" t="s">
+      <c r="A36" t="s">
         <v>128</v>
       </c>
       <c r="B36" s="12" t="s">
@@ -2365,39 +2374,39 @@
         <v>2020</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F36" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="G36" t="s">
-        <v>15</v>
-      </c>
-      <c r="J36" t="s">
+        <v>106</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J36" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="37" s="0" customFormat="1" ht="25.5">
-      <c r="A37" t="s">
-        <v>130</v>
+      <c r="A37" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C37">
         <v>2020</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>15</v>
@@ -2413,17 +2422,17 @@
       <c r="B38" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="4">
         <v>2020</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F38" s="27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>15</v>
@@ -2434,22 +2443,22 @@
     </row>
     <row r="39" s="0" customFormat="1" ht="25.5">
       <c r="A39" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="C39" s="4">
+        <v>137</v>
+      </c>
+      <c r="C39">
         <v>2020</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F39" s="27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>15</v>
@@ -2460,36 +2469,36 @@
     </row>
     <row r="40" s="0" customFormat="1" ht="25.5">
       <c r="A40" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="C40">
-        <v>2020</v>
+        <v>140</v>
+      </c>
+      <c r="C40" s="12">
+        <v>2010</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>140</v>
+        <v>27</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F40" s="27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>15</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>46</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41" s="0" customFormat="1" ht="25.5">
       <c r="A41" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C41" s="12">
         <v>2010</v>
@@ -2498,111 +2507,108 @@
         <v>27</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F41" s="27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>15</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="42" s="0" customFormat="1" ht="25.5">
-      <c r="A42" s="12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25">
+      <c r="A42" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="C42" s="12">
-        <v>2010</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>27</v>
+      <c r="C42" t="s">
+        <v>146</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="F42" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="43" ht="14.25">
-      <c r="A43" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G42" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" ht="25.5">
+      <c r="A43" t="s">
+        <v>149</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="C43" t="s">
         <v>146</v>
       </c>
-      <c r="B43" s="28" t="s">
+      <c r="E43" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C43" t="s">
+      <c r="F43" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="F43" s="27" t="s">
-        <v>150</v>
-      </c>
       <c r="G43" t="s">
-        <v>21</v>
+        <v>15</v>
+      </c>
+      <c r="H43" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="I43" s="19" t="s">
+        <v>87</v>
       </c>
       <c r="J43" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="44" ht="25.5">
+    <row r="44" ht="14.25">
       <c r="A44" t="s">
         <v>151</v>
       </c>
-      <c r="B44" s="28" t="s">
+      <c r="B44" t="s">
         <v>152</v>
       </c>
       <c r="C44" t="s">
+        <v>146</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F44" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="F44" s="27" t="s">
-        <v>150</v>
-      </c>
       <c r="G44" t="s">
-        <v>15</v>
-      </c>
-      <c r="H44" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="I44" s="19" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J44" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="45" ht="14.25">
-      <c r="A45" t="s">
+      <c r="A45" s="2" t="s">
         <v>153</v>
       </c>
       <c r="B45" t="s">
         <v>154</v>
       </c>
       <c r="C45" t="s">
+        <v>146</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F45" s="27" t="s">
         <v>148</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="F45" s="27" t="s">
-        <v>150</v>
       </c>
       <c r="G45" t="s">
         <v>21</v>
@@ -2612,23 +2618,23 @@
       </c>
     </row>
     <row r="46" ht="14.25">
-      <c r="A46" s="2" t="s">
+      <c r="A46" t="s">
         <v>155</v>
       </c>
       <c r="B46" t="s">
         <v>156</v>
       </c>
       <c r="C46" t="s">
+        <v>146</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F46" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="F46" s="27" t="s">
-        <v>150</v>
-      </c>
       <c r="G46" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J46" t="s">
         <v>46</v>
@@ -2641,110 +2647,113 @@
       <c r="B47" t="s">
         <v>158</v>
       </c>
-      <c r="C47" t="s">
-        <v>148</v>
+      <c r="C47">
+        <v>2025</v>
+      </c>
+      <c r="D47" t="s">
+        <v>159</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="F47" s="27" t="s">
-        <v>150</v>
+        <v>42</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="G47" t="s">
         <v>15</v>
       </c>
+      <c r="H47" t="s">
+        <v>99</v>
+      </c>
+      <c r="I47" t="s">
+        <v>100</v>
+      </c>
       <c r="J47" t="s">
-        <v>46</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48" ht="14.25">
-      <c r="A48" t="s">
+      <c r="A48" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B48" t="s">
+        <v>163</v>
+      </c>
+      <c r="C48">
+        <v>2026</v>
+      </c>
+      <c r="D48" t="s">
         <v>159</v>
       </c>
-      <c r="B48" t="s">
-        <v>160</v>
-      </c>
-      <c r="C48">
-        <v>2025</v>
-      </c>
-      <c r="D48" t="s">
-        <v>161</v>
-      </c>
       <c r="E48" s="1" t="s">
-        <v>42</v>
+        <v>164</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G48" t="s">
         <v>15</v>
       </c>
-      <c r="H48" t="s">
-        <v>101</v>
-      </c>
-      <c r="I48" t="s">
-        <v>102</v>
-      </c>
       <c r="J48" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" ht="14.25">
       <c r="A49" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B49" t="s">
+        <v>168</v>
+      </c>
+      <c r="C49" s="4">
+        <v>2026</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B49" t="s">
+      <c r="F49" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C49">
-        <v>2026</v>
-      </c>
-      <c r="D49" t="s">
-        <v>161</v>
-      </c>
-      <c r="E49" s="1" t="s">
+      <c r="G49" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" t="s">
+        <v>99</v>
+      </c>
+      <c r="J49" t="s">
         <v>166</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G49" t="s">
-        <v>15</v>
-      </c>
-      <c r="J49" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="50" ht="14.25">
       <c r="A50" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B50" t="s">
         <v>170</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>171</v>
       </c>
       <c r="C50" s="4">
         <v>2026</v>
       </c>
-      <c r="D50" s="12" t="s">
-        <v>171</v>
+      <c r="D50" t="s">
+        <v>159</v>
       </c>
       <c r="E50" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G50" t="s">
+        <v>15</v>
+      </c>
+      <c r="J50" t="s">
         <v>166</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G50" t="s">
-        <v>15</v>
-      </c>
-      <c r="H50" t="s">
-        <v>101</v>
-      </c>
-      <c r="J50" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="51" ht="14.25">
+    </row>
+    <row r="51" ht="28.5">
       <c r="A51" s="4" t="s">
         <v>172</v>
       </c>
@@ -2755,261 +2764,255 @@
         <v>2026</v>
       </c>
       <c r="D51" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="E51" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G51" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J51" t="s">
         <v>166</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G51" t="s">
-        <v>15</v>
-      </c>
-      <c r="J51" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="52" ht="28.5">
       <c r="A52" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B52" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="C52" s="4">
-        <v>2026</v>
+      <c r="B52" t="s">
+        <v>176</v>
+      </c>
+      <c r="C52" t="s">
+        <v>177</v>
       </c>
       <c r="D52" t="s">
-        <v>171</v>
+        <v>27</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G52" t="s">
         <v>15</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J52" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" ht="28.5">
       <c r="A53" s="4" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B53" t="s">
-        <v>178</v>
-      </c>
-      <c r="C53" t="s">
-        <v>179</v>
+        <v>183</v>
+      </c>
+      <c r="C53">
+        <v>2025</v>
       </c>
       <c r="D53" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G53" t="s">
         <v>15</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="J53" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="54" ht="28.5">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="54" ht="14.25">
       <c r="A54" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B54" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C54">
+        <v>2020</v>
+      </c>
+      <c r="D54" t="s">
+        <v>190</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J54" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="55" ht="14.25">
+      <c r="A55" t="s">
+        <v>193</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="C55" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D55" t="s">
+        <v>190</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" t="s">
+        <v>195</v>
+      </c>
+      <c r="J55" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="56" ht="14.25">
+      <c r="A56" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B56" t="s">
+        <v>197</v>
+      </c>
+      <c r="C56">
         <v>2025</v>
       </c>
-      <c r="D54" t="s">
-        <v>186</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G54" t="s">
-        <v>15</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="J54" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="55" ht="14.25">
-      <c r="A55" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B55" t="s">
-        <v>191</v>
-      </c>
-      <c r="C55">
-        <v>2020</v>
-      </c>
-      <c r="D55" t="s">
-        <v>192</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J55" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="56" ht="14.25">
-      <c r="A56" t="s">
-        <v>195</v>
-      </c>
-      <c r="B56" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="C56" s="4">
-        <v>2020</v>
-      </c>
-      <c r="D56" t="s">
-        <v>192</v>
-      </c>
       <c r="E56" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H56" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J56" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57" ht="14.25">
       <c r="A57" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C57" s="4">
+        <v>2025</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B57" t="s">
+      <c r="F57" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C57">
-        <v>2025</v>
-      </c>
-      <c r="E57" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="F57" s="29" t="s">
-        <v>201</v>
-      </c>
       <c r="J57" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" ht="14.25">
       <c r="A58" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="B58" s="30" t="s">
+      <c r="B58" s="12" t="s">
         <v>203</v>
       </c>
       <c r="C58" s="4">
         <v>2025</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J58" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59" ht="14.25">
       <c r="A59" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="B59" s="30" t="s">
+      <c r="B59" t="s">
         <v>205</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59">
         <v>2025</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J59" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" ht="14.25">
       <c r="A60" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B60" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C60">
+        <v>2026</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J60" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="61" ht="14.25">
+      <c r="A61" t="s">
+        <v>212</v>
+      </c>
+      <c r="B61" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="C61">
         <v>2025</v>
       </c>
-      <c r="E60" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="J60" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="61" ht="14.25">
-      <c r="A61" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B61" t="s">
-        <v>210</v>
-      </c>
-      <c r="C61">
-        <v>2026</v>
-      </c>
-      <c r="E61" s="29" t="s">
+      <c r="E61" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="F61" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="J61" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="J61" t="s">
-        <v>213</v>
       </c>
     </row>
   </sheetData>
